--- a/hsk-lesson-template.xlsx
+++ b/hsk-lesson-template.xlsx
@@ -15,52 +15,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="1">
     <fill>
       <patternFill patternType="none"/>
     </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -142,91 +117,169 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Ảnh minh hoạ — điền imagekeyword (một từ TIẾNG ANH, vd 'apple') thì hệ thống tự tìm ảnh.</t>
+          <t xml:space="preserve">• Ảnh minh hoạ — hệ thống tự tìm cho MỌI từ, kể cả khi bỏ trống imagekeyword</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Từ trừu tượng (没关系, 对不起) nên để trống, tránh ảnh minh hoạ vô nghĩa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t xml:space="preserve">     (khi đó nó tìm theo nghĩa tiếng Việt). Muốn ảnh chuẩn hơn thì điền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     imagekeyword bằng một từ TIẾNG ANH, vd 'apple', 'teacher', 'running'.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÁC SHEET:</t>
+          <t xml:space="preserve">     Ảnh nào hệ thống tự đoán sẽ bị đánh dấu "nên xem lại" trong bảng kiểm tra;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">• LessonInfo  — mỗi dòng một cặp: tên trường ở cột A, giá trị ở cột B.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Vocabulary  — mỗi dòng một từ. example1/example2 là câu ví dụ, kèm bản dịch ở cột _vi.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">     thầy thay ảnh khác bằng cách dán (⌘V) hoặc kéo thả ngay trong mục ✏️.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Reading     — bài đọc (không bắt buộc). Nhiều dòng sẽ nối thành nhiều đoạn.</t>
+          <t xml:space="preserve">CÁC SHEET:</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Grammar     — các dòng CÙNG số order gộp thành MỘT điểm ngữ pháp, mỗi dòng thêm một ví dụ.</t>
+          <t xml:space="preserve">• LessonInfo  — mỗi dòng một cặp: tên trường ở cột A, giá trị ở cột B.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">• GrammarPractice / VocabPractice — mỗi dòng một câu luyện tập.</t>
+          <t xml:space="preserve">• Vocabulary  — mỗi dòng một từ. example1/example2 là câu ví dụ, kèm bản dịch ở cột _vi.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">     type nhận: mcq · fill · arrange · correct · structure (ngữ pháp)</t>
+          <t xml:space="preserve">• Reading     — bài đọc (không bắt buộc). Hội thoại thì điền cột speaker.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">                mcq · match · picture · pinyin · cloze · complete (từ vựng)</t>
+          <t xml:space="preserve">• Grammar     — các dòng CÙNG số order gộp thành MỘT điểm ngữ pháp, mỗi dòng thêm một ví dụ.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">• GrammarPractice / VocabPractice — bài luyện tập (xem bên dưới).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t xml:space="preserve">• Radicals    — bộ thủ (không bắt buộc). Sheet trống thì mục Bộ thủ tự ẩn khỏi bài giảng.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sheet nào để trống thì mục tương ứng tự biến mất khỏi DANH MỤC BÀI HỌC.</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SÁU LOẠI BÀI LUYỆN TẬP — tất cả đều bấm được, chấm ngay tại lớp:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• mcq       Chọn đáp án. Điền a, b, c, d và answer = A/B/C/D.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• fill      Điền vào chỗ trống. Viết ______ trong question, answer là chữ cần điền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              Nhiều đáp án đúng thì ngăn bằng dấu / — vd: 没关系 / 不客气</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• arrange   Sắp xếp câu. tokens = các thẻ ngăn bằng dấu / (vd: 好 / 你), answer = câu đúng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• match     Nối từ. MỖI DÒNG một cặp: left = từ, right = nghĩa. Các dòng liền nhau gộp thành một bài.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• pinyin    Nối chữ Hán với pinyin. Dùng left/right, HOẶC để trống hết — hệ thống tự lấy từ vựng của bài.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• picture   Nhìn hình chọn từ. Để trống hết là hệ thống tự dùng những từ đã có ảnh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ghi sai tên loại cũng không sao: multiple_choice, fill_blank, sap_xep, noi_tu… đều hiểu được.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dòng nào thiếu đáp án thì bảng kiểm tra báo và bài đó không lên slide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet nào để trống thì mục tương ứng tự biến mất khỏi DANH MỤC BÀI HỌC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t xml:space="preserve">Các dòng ví dụ bên dưới lấy từ bài mẫu Bài 1 — xoá và thay bằng bài của thầy.</t>
         </is>
@@ -1180,7 +1233,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type: mcq · fill · arrange · correct · structure. answer là A/B/C/D với câu trắc nghiệm.</t>
+          <t xml:space="preserve">Sáu loại: mcq · fill · arrange · match · pinyin · picture. Xem sheet Instructions.</t>
         </is>
       </c>
     </row>
@@ -1232,6 +1285,16 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t xml:space="preserve">tokens</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">explanation</t>
         </is>
       </c>
@@ -1239,7 +1302,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_choice</t>
+          <t xml:space="preserve">mcq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1272,7 +1335,7 @@
           <t xml:space="preserve">B</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Chào thầy cô giáo cần dùng đại từ kính trọng "您" (nín).</t>
         </is>
@@ -1281,7 +1344,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_choice</t>
+          <t xml:space="preserve">mcq</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1314,9 +1377,58 @@
           <t xml:space="preserve">B</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Thêm hậu tố 们 vào sau 你 ta được 你们 (nǐmen).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arrange</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sắp xếp thành câu chào đúng:</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你好</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">好 / 你</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tính từ 好 đứng sau đại từ 你 tạo thành lời chào 你好.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fill</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hoàn thành hội thoại: A: 对不起！ B: ______！</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没关系 / 不客气</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khi ai đó nói "对不起" (xin lỗi), ta đáp lại bằng "没关系" (không sao).</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1442,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type: mcq · match · picture · pinyin · cloze · complete. Với match, mỗi dòng một cặp left/right.</t>
+          <t xml:space="preserve">match / pinyin / picture: mỗi dòng một cặp; để trống hết left-right là hệ thống tự lấy từ vựng của bài.</t>
         </is>
       </c>
     </row>
@@ -1382,6 +1494,16 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t xml:space="preserve">tokens</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">explanation</t>
         </is>
       </c>
@@ -1389,85 +1511,139 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill_blank</t>
+          <t xml:space="preserve">mcq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoàn thành hội thoại lịch sự sau: A: 对不起！
-B: ______ ！</t>
+          <t xml:space="preserve">Từ "对不起" có nghĩa là gì?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">你好</t>
+          <t xml:space="preserve">Xin chào</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">没关系</t>
+          <t xml:space="preserve">Cảm ơn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">再见</t>
+          <t xml:space="preserve">Xin lỗi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">谢谢</t>
+          <t xml:space="preserve">Không sao</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">B</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Khi ai đó nói "对不起" (xin lỗi), ta đáp lại bằng "没关系" (không sao).</t>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对不起 (duìbuqǐ) = Xin lỗi.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">matching</t>
+          <t xml:space="preserve">match</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nối từ Tiếng Trung với nghĩa Tiếng Việt đúng: Từ "对不起" có nghĩa là gì?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Xin chào</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cảm ơn</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Xin lỗi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Không sao</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">对不起 (duìbuqǐ) = Xin lỗi.</t>
+          <t xml:space="preserve">Nối từ tiếng Trung với nghĩa tiếng Việt:</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anh, chị, bạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">match</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">您</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ông, bà, ngài (lịch sự)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">match</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没关系</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">không sao, không có gì</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">match</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对不起</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xin lỗi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pinyin</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nối chữ Hán với pinyin đúng:</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">picture</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhìn hình, chọn từ đúng:</t>
         </is>
       </c>
     </row>
